--- a/data/actions/action_database.xlsx
+++ b/data/actions/action_database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/actions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C76B585-A2A5-8A46-BF87-129AE7B17651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BAEA85-DBBB-2741-B68B-BDE3D903056C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40" yWindow="500" windowWidth="35840" windowHeight="21900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actions" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="309">
   <si>
     <t>source</t>
   </si>
@@ -780,9 +780,6 @@
     <t>Establish fishermen controlled resilience fund</t>
   </si>
   <si>
-    <t>Improve fisheries management / relax regulations</t>
-  </si>
-  <si>
     <t>Modify permit structure (e.g., cost, who qualifies)</t>
   </si>
   <si>
@@ -952,6 +949,9 @@
   </si>
   <si>
     <t>Wealth and reserves, Mobility</t>
+  </si>
+  <si>
+    <t>responsibility</t>
   </si>
 </sst>
 </file>
@@ -1290,16 +1290,16 @@
         <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1322,7 +1322,7 @@
         <v>75</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1345,7 +1345,7 @@
         <v>75</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1368,7 +1368,7 @@
         <v>75</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1391,7 +1391,7 @@
         <v>75</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1414,7 +1414,7 @@
         <v>75</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1437,7 +1437,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1460,7 +1460,7 @@
         <v>75</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1483,7 +1483,7 @@
         <v>75</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1506,7 +1506,7 @@
         <v>75</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1529,7 +1529,7 @@
         <v>75</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1552,7 +1552,7 @@
         <v>75</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1575,7 +1575,7 @@
         <v>75</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1612,7 +1612,7 @@
         <v>61</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -1632,7 +1632,7 @@
         <v>63</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -1672,7 +1672,7 @@
         <v>180</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -1692,7 +1692,7 @@
         <v>219</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -1723,19 +1723,19 @@
         <v>1</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="C21" s="3">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1743,13 +1743,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C22" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>250</v>
@@ -1763,13 +1763,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C23" s="3">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>250</v>
@@ -1779,23 +1779,23 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>77</v>
+      <c r="A24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="3">
+        <v>38</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1803,13 +1803,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>77</v>
@@ -1820,36 +1820,36 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C26">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>83</v>
@@ -1860,36 +1860,36 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B29" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>29</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C29" s="3">
-        <v>7</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>84</v>
@@ -1899,43 +1899,43 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" s="3">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B31" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>11</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C31" s="3">
-        <v>23</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1943,256 +1943,253 @@
         <v>1</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="C32" s="3">
+        <v>54</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" s="3">
+        <v>55</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C34" s="3">
+        <v>57</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35">
+        <v>18</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="C37">
+        <v>7</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38">
+        <v>12</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39">
+        <v>13</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C33" s="3">
-        <v>25</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="7" t="s">
+      <c r="D41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C42" s="3">
+        <v>19</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C34" s="3">
-        <v>28</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35" s="3">
-        <v>31</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C36" s="3">
-        <v>50</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C37" s="3">
-        <v>51</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C38" s="3">
-        <v>5</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C39" s="3">
-        <v>4</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C40" s="3">
-        <v>54</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E40" s="3" t="s">
+      <c r="C43" s="3">
+        <v>32</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C41" s="3">
-        <v>55</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C42" s="3">
-        <v>57</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43">
-        <v>18</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>162</v>
+        <v>1</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="C44" s="3">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>165</v>
+        <v>214</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>269</v>
@@ -2201,84 +2198,84 @@
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="6" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="6" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C47">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" s="3">
+        <v>45</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2286,19 +2283,19 @@
         <v>1</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="C49" s="3">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>251</v>
+        <v>274</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2306,39 +2303,39 @@
         <v>1</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="C50" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C51" s="3">
-        <v>19</v>
-      </c>
-      <c r="D51" s="3" t="s">
+      <c r="A51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51">
         <v>2</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>268</v>
+      <c r="D51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2346,39 +2343,39 @@
         <v>1</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C52" s="3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>268</v>
+        <v>209</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C53" s="3">
-        <v>40</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>270</v>
+      <c r="A53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53">
+        <v>6</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2389,16 +2386,16 @@
         <v>36</v>
       </c>
       <c r="C54">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>273</v>
+        <v>48</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2409,116 +2406,116 @@
         <v>6</v>
       </c>
       <c r="C55">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>273</v>
+        <v>17</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="6" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C56">
+        <v>9</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57">
         <v>10</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C57" s="3">
-        <v>45</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>220</v>
+      <c r="D57" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>230</v>
+        <v>159</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="C58" s="3">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>275</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C59" s="3">
-        <v>29</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>201</v>
+      <c r="A59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>275</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="6" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C60">
-        <v>2</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>78</v>
+        <v>4</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2526,39 +2523,39 @@
         <v>1</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C61" s="3">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>78</v>
+        <v>101</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62">
-        <v>6</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>79</v>
+      <c r="A62" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" s="3">
+        <v>10</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2569,36 +2566,36 @@
         <v>36</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>82</v>
+        <v>37</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>280</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="6" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C64">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>82</v>
+        <v>38</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2609,16 +2606,16 @@
         <v>36</v>
       </c>
       <c r="C65">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>276</v>
+        <v>39</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>278</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2629,133 +2626,133 @@
         <v>36</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C67" s="3">
-        <v>1</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>161</v>
+      <c r="A67" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C67">
+        <v>5</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C68">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69">
+        <v>7</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70">
+        <v>8</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71">
         <v>5</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69">
-        <v>4</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C70" s="3">
-        <v>17</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C71" s="3">
-        <v>10</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="F71" s="6" t="s">
+      <c r="D71" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="6" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>281</v>
+        <v>7</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>73</v>
@@ -2763,19 +2760,19 @@
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="6" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>278</v>
+        <v>8</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>73</v>
@@ -2783,19 +2780,19 @@
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="6" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>73</v>
@@ -2803,96 +2800,96 @@
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="6" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>283</v>
+        <v>12</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C76">
-        <v>5</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>41</v>
+      <c r="A76" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C76" s="3">
+        <v>8</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C77">
-        <v>6</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>42</v>
+      <c r="A77" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" s="3">
+        <v>9</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C78">
-        <v>7</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>43</v>
+      <c r="A78" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" s="3">
+        <v>11</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C79">
-        <v>8</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>44</v>
+      <c r="A79" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C79" s="3">
+        <v>12</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>282</v>
@@ -2902,17 +2899,17 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C80">
-        <v>5</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>91</v>
+      <c r="A80" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="3">
+        <v>13</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>73</v>
@@ -2922,80 +2919,80 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>73</v>
+      <c r="A81" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" s="3">
+        <v>14</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82">
-        <v>2</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>73</v>
+      <c r="A82" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="3">
+        <v>15</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>278</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83">
-        <v>3</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>9</v>
+      <c r="A83" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" s="3">
+        <v>16</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84">
-        <v>6</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>73</v>
+      <c r="A84" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" s="3">
+        <v>18</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>281</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>73</v>
@@ -3006,16 +3003,16 @@
         <v>1</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="C85" s="3">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>281</v>
+        <v>210</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>73</v>
@@ -3026,16 +3023,16 @@
         <v>1</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="C86" s="3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>94</v>
+        <v>211</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>73</v>
@@ -3046,16 +3043,16 @@
         <v>1</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="C87" s="3">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>73</v>
@@ -3066,16 +3063,16 @@
         <v>1</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C88" s="3">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>283</v>
+        <v>229</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>73</v>
@@ -3086,13 +3083,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
       <c r="C89" s="3">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>73</v>
@@ -3102,103 +3099,103 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C90" s="3">
-        <v>14</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>280</v>
+      <c r="A90" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90">
+        <v>13</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>285</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C91" s="3">
-        <v>15</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>100</v>
+      <c r="A91" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C91">
+        <v>21</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C92" s="3">
-        <v>16</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>98</v>
+      <c r="A92" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92">
+        <v>5</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>183</v>
+        <v>159</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C93" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>282</v>
+        <v>163</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C94" s="3">
-        <v>36</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>210</v>
+      <c r="A94" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3206,19 +3203,19 @@
         <v>1</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C95" s="3">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>73</v>
+        <v>270</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3226,193 +3223,196 @@
         <v>1</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>245</v>
+        <v>190</v>
       </c>
       <c r="C96" s="3">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B97" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" s="3">
+        <v>24</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C98" s="3">
+        <v>25</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B99" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C97" s="3">
-        <v>52</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C98" s="3">
-        <v>62</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="6" t="s">
+      <c r="C99" s="3">
+        <v>28</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C100" s="3">
+        <v>31</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C101" s="3">
+        <v>50</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" s="3">
+        <v>51</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C103" s="3">
+        <v>5</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C104" s="3">
+        <v>4</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B105" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C99">
-        <v>13</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C100">
-        <v>21</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101">
-        <v>5</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C102" s="3">
-        <v>2</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C104">
+      <c r="C105">
         <v>23</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D105" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C105">
-        <v>10</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>158</v>
@@ -3421,18 +3421,18 @@
         <v>158</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C106" s="3">
-        <v>34</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>208</v>
+    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106">
+        <v>10</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>158</v>
@@ -3441,27 +3441,27 @@
         <v>158</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C107">
-        <v>14</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>290</v>
+    <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C107" s="3">
+        <v>34</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="6" t="s">
         <v>35</v>
       </c>
@@ -3469,19 +3469,19 @@
         <v>36</v>
       </c>
       <c r="C108">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>291</v>
+        <v>50</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="6" t="s">
         <v>35</v>
       </c>
@@ -3489,19 +3489,19 @@
         <v>36</v>
       </c>
       <c r="C109">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="6" t="s">
         <v>35</v>
       </c>
@@ -3509,19 +3509,19 @@
         <v>36</v>
       </c>
       <c r="C110">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>289</v>
+        <v>55</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>290</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="6" t="s">
         <v>35</v>
       </c>
@@ -3529,79 +3529,79 @@
         <v>36</v>
       </c>
       <c r="C111">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>291</v>
+        <v>56</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B112" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C112">
         <v>24</v>
       </c>
-      <c r="C112">
-        <v>4</v>
-      </c>
       <c r="D112" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C113" s="3">
-        <v>2</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>176</v>
+    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C114" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="3" t="s">
         <v>1</v>
       </c>
@@ -3609,59 +3609,59 @@
         <v>185</v>
       </c>
       <c r="C115" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>293</v>
+        <v>186</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B116" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C116" s="3">
+        <v>21</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A117" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B117" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C116" s="3">
+      <c r="C117" s="3">
         <v>30</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D117" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E116" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="F116" s="3" t="s">
+      <c r="E117" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F117" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A117" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C117" s="3">
-        <v>46</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="3" t="s">
         <v>1</v>
       </c>
@@ -3669,110 +3669,110 @@
         <v>215</v>
       </c>
       <c r="C118" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="C119" s="3">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A120" s="6" t="s">
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C120" s="3">
+        <v>56</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A121" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C121" s="3">
+        <v>41</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A122" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B122" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C120">
+      <c r="C122">
         <v>11</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="D122" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E120" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A121" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C121">
-        <v>17</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C122" s="3">
-        <v>5</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="E122" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C123">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>81</v>
@@ -3781,130 +3781,124 @@
         <v>81</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A124" s="6" t="s">
+    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C124" s="3">
         <v>5</v>
       </c>
-      <c r="B124" s="6" t="s">
+      <c r="D124" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A125" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125">
+        <v>15</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B126" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C124">
+      <c r="C126">
         <v>7</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D126" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="E126" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F124" s="2" t="s">
+      <c r="F126" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A125" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B125" s="7" t="s">
+    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A127" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B127" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C125" s="3">
+      <c r="C127" s="3">
         <v>48</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D127" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E127" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="F127" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A126" s="6" t="s">
+    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A128" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="B128" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C126">
+      <c r="C128">
         <v>16</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="D128" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="E128" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F126" s="2" t="s">
+      <c r="F128" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A127" s="6" t="s">
+    <row r="129" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A129" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B127" s="6" t="s">
+      <c r="B129" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C127">
+      <c r="C129">
         <v>28</v>
       </c>
-      <c r="D127" s="6" t="s">
+      <c r="D129" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E129" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F127" s="2" t="s">
+      <c r="F129" s="2" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C128" s="3">
-        <v>39</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A129" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C129" s="3">
-        <v>6</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G129" s="6" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3912,111 +3906,121 @@
         <v>1</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C130" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>89</v>
+        <v>213</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G130" s="6" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>223</v>
+        <v>159</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C131" s="3">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>253</v>
+        <v>172</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>253</v>
+        <v>172</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G131" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G131" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G131">
+      <sortCondition ref="F1:F131"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F83">
     <sortCondition ref="A2:A83"/>
     <sortCondition ref="C2:C83"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B49" r:id="rId1" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{5C0C1454-402C-5344-8CE1-3D8C78C0E6CE}"/>
-    <hyperlink ref="B113" r:id="rId2" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{E93958B3-D035-774B-B2B5-29763C0F8B90}"/>
-    <hyperlink ref="B50" r:id="rId3" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{3BF5C0BF-380B-7440-894B-F22E531FDA9A}"/>
-    <hyperlink ref="B39" r:id="rId4" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{628F5983-AD30-B64F-BA19-D335C3D124E8}"/>
-    <hyperlink ref="B38" r:id="rId5" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{6C9323A9-8057-6243-8938-13F4CBADE6F6}"/>
+    <hyperlink ref="B95" r:id="rId1" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{5C0C1454-402C-5344-8CE1-3D8C78C0E6CE}"/>
+    <hyperlink ref="B114" r:id="rId2" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{E93958B3-D035-774B-B2B5-29763C0F8B90}"/>
+    <hyperlink ref="B41" r:id="rId3" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{3BF5C0BF-380B-7440-894B-F22E531FDA9A}"/>
+    <hyperlink ref="B104" r:id="rId4" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{628F5983-AD30-B64F-BA19-D335C3D124E8}"/>
+    <hyperlink ref="B103" r:id="rId5" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{6C9323A9-8057-6243-8938-13F4CBADE6F6}"/>
     <hyperlink ref="B18" r:id="rId6" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{892986EB-2DDB-F04F-9C69-C48539130662}"/>
-    <hyperlink ref="B21" r:id="rId7" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{3C1549C8-EA68-1544-AA21-636B7521DDDD}"/>
-    <hyperlink ref="B85" r:id="rId8" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{C667FD88-B8F7-9546-8C19-366B2852D70E}"/>
-    <hyperlink ref="B86" r:id="rId9" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{18514548-5808-9E4D-B0EF-A1364CA93F96}"/>
-    <hyperlink ref="B71" r:id="rId10" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{942F7DBE-BCC9-2E4A-B48E-C9FF164826E8}"/>
-    <hyperlink ref="B87" r:id="rId11" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{DEF3634D-67ED-FC4C-B2E8-AB953310D339}"/>
-    <hyperlink ref="B88" r:id="rId12" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{DB7BCFD5-B3C5-F641-8E19-C110B44076D3}"/>
-    <hyperlink ref="B89" r:id="rId13" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{BE537C08-AFA5-2342-9C90-8297D5653465}"/>
-    <hyperlink ref="B90" r:id="rId14" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{AE941CA9-AB35-6942-87B1-A34DE3CE4010}"/>
-    <hyperlink ref="B91" r:id="rId15" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{81D36874-A55A-7A43-8BF2-71E9D3D05EE0}"/>
-    <hyperlink ref="B92" r:id="rId16" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{0BDC768D-0D3C-324D-9B8A-137D557663B4}"/>
-    <hyperlink ref="B70" r:id="rId17" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{C7E96F08-D409-BD49-B620-45CB4A7A5264}"/>
-    <hyperlink ref="B93" r:id="rId18" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{555572C8-AFAD-264D-AD73-C3A0D2246E6D}"/>
-    <hyperlink ref="B51" r:id="rId19" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{1FB7C0E8-5B14-DA4F-96A4-8262500349C1}"/>
-    <hyperlink ref="B114" r:id="rId20" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{57B9CA4D-6F46-B848-916A-9472408EC072}"/>
-    <hyperlink ref="B115" r:id="rId21" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{1CA15F5C-3DBB-3E4A-9FA8-0887A59C15AA}"/>
-    <hyperlink ref="B22" r:id="rId22" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{1B615AC8-9293-524C-BC48-C0D88383A11A}"/>
-    <hyperlink ref="B31" r:id="rId23" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{A8E26BEA-2432-4B49-B232-7267E60AD88B}"/>
-    <hyperlink ref="B32" r:id="rId24" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{9887D830-014D-5244-8383-83140642CDCD}"/>
-    <hyperlink ref="B33" r:id="rId25" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{003D387A-A2C7-7A4D-9848-0052DD8DB101}"/>
+    <hyperlink ref="B22" r:id="rId7" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{3C1549C8-EA68-1544-AA21-636B7521DDDD}"/>
+    <hyperlink ref="B76" r:id="rId8" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{C667FD88-B8F7-9546-8C19-366B2852D70E}"/>
+    <hyperlink ref="B77" r:id="rId9" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{18514548-5808-9E4D-B0EF-A1364CA93F96}"/>
+    <hyperlink ref="B62" r:id="rId10" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{942F7DBE-BCC9-2E4A-B48E-C9FF164826E8}"/>
+    <hyperlink ref="B78" r:id="rId11" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{DEF3634D-67ED-FC4C-B2E8-AB953310D339}"/>
+    <hyperlink ref="B79" r:id="rId12" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{DB7BCFD5-B3C5-F641-8E19-C110B44076D3}"/>
+    <hyperlink ref="B80" r:id="rId13" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{BE537C08-AFA5-2342-9C90-8297D5653465}"/>
+    <hyperlink ref="B81" r:id="rId14" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{AE941CA9-AB35-6942-87B1-A34DE3CE4010}"/>
+    <hyperlink ref="B82" r:id="rId15" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{81D36874-A55A-7A43-8BF2-71E9D3D05EE0}"/>
+    <hyperlink ref="B83" r:id="rId16" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{0BDC768D-0D3C-324D-9B8A-137D557663B4}"/>
+    <hyperlink ref="B61" r:id="rId17" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{C7E96F08-D409-BD49-B620-45CB4A7A5264}"/>
+    <hyperlink ref="B84" r:id="rId18" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{555572C8-AFAD-264D-AD73-C3A0D2246E6D}"/>
+    <hyperlink ref="B42" r:id="rId19" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{1FB7C0E8-5B14-DA4F-96A4-8262500349C1}"/>
+    <hyperlink ref="B115" r:id="rId20" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{57B9CA4D-6F46-B848-916A-9472408EC072}"/>
+    <hyperlink ref="B116" r:id="rId21" display="https://docs.google.com/document/d/14mX6re4PwB6moM2atRMsxAtkzI0TJhcNdrCd0YZ-Ig8/edit?tab=t.0" xr:uid="{1CA15F5C-3DBB-3E4A-9FA8-0887A59C15AA}"/>
+    <hyperlink ref="B23" r:id="rId22" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{1B615AC8-9293-524C-BC48-C0D88383A11A}"/>
+    <hyperlink ref="B96" r:id="rId23" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{A8E26BEA-2432-4B49-B232-7267E60AD88B}"/>
+    <hyperlink ref="B97" r:id="rId24" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{9887D830-014D-5244-8383-83140642CDCD}"/>
+    <hyperlink ref="B98" r:id="rId25" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{003D387A-A2C7-7A4D-9848-0052DD8DB101}"/>
     <hyperlink ref="B4" r:id="rId26" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{975EDBBB-D509-FE4F-A15F-3D85952A08F1}"/>
     <hyperlink ref="B5" r:id="rId27" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{43C7F986-1F11-C845-991C-FF49EE217FF4}"/>
-    <hyperlink ref="B34" r:id="rId28" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{68E7E1E0-5781-AA41-8B32-CC30AD6FB93D}"/>
-    <hyperlink ref="B59" r:id="rId29" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{FD273EF6-B233-F449-9086-7612B89797A5}"/>
-    <hyperlink ref="B116" r:id="rId30" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{8846555E-0E64-C44B-B61A-5616922AC1F7}"/>
-    <hyperlink ref="B35" r:id="rId31" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{4102B9FC-58F7-A440-AB54-481B95E550E8}"/>
-    <hyperlink ref="B52" r:id="rId32" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{CD08D37E-EFE4-004F-83E5-398BED738AB0}"/>
+    <hyperlink ref="B99" r:id="rId28" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{68E7E1E0-5781-AA41-8B32-CC30AD6FB93D}"/>
+    <hyperlink ref="B50" r:id="rId29" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{FD273EF6-B233-F449-9086-7612B89797A5}"/>
+    <hyperlink ref="B117" r:id="rId30" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{8846555E-0E64-C44B-B61A-5616922AC1F7}"/>
+    <hyperlink ref="B100" r:id="rId31" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{4102B9FC-58F7-A440-AB54-481B95E550E8}"/>
+    <hyperlink ref="B43" r:id="rId32" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{CD08D37E-EFE4-004F-83E5-398BED738AB0}"/>
     <hyperlink ref="B6" r:id="rId33" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{2E19FB82-5235-4948-8F0A-42FF31D82FA6}"/>
-    <hyperlink ref="B106" r:id="rId34" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{88E4358F-4142-AA4C-AEE4-E2B4A39BF8B6}"/>
-    <hyperlink ref="B61" r:id="rId35" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{EBD6D658-26C6-B44C-99C7-D19F7E430C77}"/>
-    <hyperlink ref="B94" r:id="rId36" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{56AD990A-0B79-3B4A-93E6-23EB85E3D586}"/>
-    <hyperlink ref="B95" r:id="rId37" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{A5EFA755-AE4A-B342-84EC-4839BE282E40}"/>
-    <hyperlink ref="B23" r:id="rId38" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{69290B11-9F88-3447-8122-F1829E29154A}"/>
-    <hyperlink ref="B128" r:id="rId39" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{2D0ADF69-57A6-254C-A394-E75D5999C677}"/>
-    <hyperlink ref="B53" r:id="rId40" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{A8193B9B-5974-9D4D-90C6-29896396D839}"/>
-    <hyperlink ref="B130" r:id="rId41" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{DC6408E0-BBDF-3B40-B62C-8DB629BF9F19}"/>
+    <hyperlink ref="B107" r:id="rId34" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{88E4358F-4142-AA4C-AEE4-E2B4A39BF8B6}"/>
+    <hyperlink ref="B52" r:id="rId35" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{EBD6D658-26C6-B44C-99C7-D19F7E430C77}"/>
+    <hyperlink ref="B85" r:id="rId36" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{56AD990A-0B79-3B4A-93E6-23EB85E3D586}"/>
+    <hyperlink ref="B86" r:id="rId37" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{A5EFA755-AE4A-B342-84EC-4839BE282E40}"/>
+    <hyperlink ref="B24" r:id="rId38" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{69290B11-9F88-3447-8122-F1829E29154A}"/>
+    <hyperlink ref="B130" r:id="rId39" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{2D0ADF69-57A6-254C-A394-E75D5999C677}"/>
+    <hyperlink ref="B44" r:id="rId40" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{A8193B9B-5974-9D4D-90C6-29896396D839}"/>
+    <hyperlink ref="B121" r:id="rId41" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{DC6408E0-BBDF-3B40-B62C-8DB629BF9F19}"/>
     <hyperlink ref="B7" r:id="rId42" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{FD361587-9A04-1A48-A1DC-186A17DC2469}"/>
     <hyperlink ref="B12" r:id="rId43" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{ABEFCA28-E6D0-944C-9FC8-1477E2B92B2F}"/>
     <hyperlink ref="B19" r:id="rId44" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{94F961B8-A2E2-B349-BD1F-609C38C735B6}"/>
-    <hyperlink ref="B57" r:id="rId45" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{0ABDA46D-7A38-D54D-9EC2-94ABF218F3D3}"/>
-    <hyperlink ref="B117" r:id="rId46" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{B880810B-A444-324D-93DA-328D3EE0BD93}"/>
-    <hyperlink ref="B118" r:id="rId47" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{F63BD98F-7363-4A44-86D0-EC7864D526F1}"/>
-    <hyperlink ref="B125" r:id="rId48" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{6F855539-16CA-C247-8FC6-8EF0D284ED03}"/>
-    <hyperlink ref="B131" r:id="rId49" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{CCB7487A-4265-2D46-8CE5-FAEA89B27F79}"/>
-    <hyperlink ref="B36" r:id="rId50" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{789824B1-60BD-3143-9602-C3EBE31994DD}"/>
-    <hyperlink ref="B37" r:id="rId51" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{4ACCE218-0E13-974D-8B3E-FB4F9A70DBDD}"/>
-    <hyperlink ref="B97" r:id="rId52" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{B992D346-59BD-464A-A0AD-08D6633BD0C2}"/>
-    <hyperlink ref="B58" r:id="rId53" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{F72F6043-26F0-5744-822E-90E1570D7CB2}"/>
-    <hyperlink ref="B40" r:id="rId54" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{22AF823B-7B01-E84B-A9BA-C679367EF74B}"/>
-    <hyperlink ref="B41" r:id="rId55" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{EEB5B3B4-C839-7C47-ADE1-268DE30D7AD4}"/>
-    <hyperlink ref="B119" r:id="rId56" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{A4094A73-20DD-F346-B245-C0E57123036E}"/>
-    <hyperlink ref="B42" r:id="rId57" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{7A128695-1439-7440-A649-C7173727F4C5}"/>
+    <hyperlink ref="B48" r:id="rId45" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{0ABDA46D-7A38-D54D-9EC2-94ABF218F3D3}"/>
+    <hyperlink ref="B118" r:id="rId46" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{B880810B-A444-324D-93DA-328D3EE0BD93}"/>
+    <hyperlink ref="B119" r:id="rId47" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{F63BD98F-7363-4A44-86D0-EC7864D526F1}"/>
+    <hyperlink ref="B127" r:id="rId48" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{6F855539-16CA-C247-8FC6-8EF0D284ED03}"/>
+    <hyperlink ref="B21" r:id="rId49" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{CCB7487A-4265-2D46-8CE5-FAEA89B27F79}"/>
+    <hyperlink ref="B101" r:id="rId50" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{789824B1-60BD-3143-9602-C3EBE31994DD}"/>
+    <hyperlink ref="B102" r:id="rId51" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{4ACCE218-0E13-974D-8B3E-FB4F9A70DBDD}"/>
+    <hyperlink ref="B88" r:id="rId52" display="https://docs.google.com/document/d/1F28G1moUbNnsuwh6p1lBqc-9czd0s7Y9/edit" xr:uid="{B992D346-59BD-464A-A0AD-08D6633BD0C2}"/>
+    <hyperlink ref="B49" r:id="rId53" display="https://docs.google.com/document/d/1xU8AoBxuE8qgzVhx3fn7b3Gm4ecfgYDUvT8k1yNAPd4/edit?tab=t.0" xr:uid="{F72F6043-26F0-5744-822E-90E1570D7CB2}"/>
+    <hyperlink ref="B32" r:id="rId54" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{22AF823B-7B01-E84B-A9BA-C679367EF74B}"/>
+    <hyperlink ref="B33" r:id="rId55" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{EEB5B3B4-C839-7C47-ADE1-268DE30D7AD4}"/>
+    <hyperlink ref="B120" r:id="rId56" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{A4094A73-20DD-F346-B245-C0E57123036E}"/>
+    <hyperlink ref="B34" r:id="rId57" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{7A128695-1439-7440-A649-C7173727F4C5}"/>
     <hyperlink ref="B8" r:id="rId58" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{0EDB7783-92F3-1045-99B5-9ECD661822D4}"/>
     <hyperlink ref="B9" r:id="rId59" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{B588D3F0-2512-B545-A927-BC41CCB671F4}"/>
     <hyperlink ref="B10" r:id="rId60" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{F2B8B728-0C28-9C4A-AD75-5C734FD37C1D}"/>
     <hyperlink ref="B13" r:id="rId61" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{2ECFFB6A-31F0-6040-B4BE-42B2BBF760CD}"/>
-    <hyperlink ref="B98" r:id="rId62" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{38B369B5-2BA0-0C41-8200-B751EA55CA63}"/>
-    <hyperlink ref="B96" r:id="rId63" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{C60521A4-3208-954A-A5F1-E8485C9FA351}"/>
+    <hyperlink ref="B89" r:id="rId62" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{38B369B5-2BA0-0C41-8200-B751EA55CA63}"/>
+    <hyperlink ref="B87" r:id="rId63" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{C60521A4-3208-954A-A5F1-E8485C9FA351}"/>
     <hyperlink ref="B11" r:id="rId64" display="https://docs.google.com/document/d/1hhqU4cqF5FrYIODpIXAOaWzdiU5zmpANKNv0OLkgS1g/edit?tab=t.0" xr:uid="{F728F815-6AC0-D24C-ADA9-B0EA9B38E6EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4038,12 +4042,14 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>308</v>
+      </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -4095,10 +4101,10 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4106,7 +4112,7 @@
         <v>250</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4153,7 +4159,7 @@
         <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D11" s="3"/>
     </row>
@@ -4189,7 +4195,7 @@
         <v>79</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D15" s="3"/>
     </row>
@@ -4207,7 +4213,7 @@
         <v>80</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D17" s="3"/>
     </row>
@@ -4216,7 +4222,7 @@
         <v>73</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D18" s="3"/>
     </row>
@@ -4225,7 +4231,7 @@
         <v>87</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D19" s="3"/>
     </row>
@@ -4246,7 +4252,7 @@
         <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D21" s="3"/>
     </row>
@@ -4264,7 +4270,7 @@
         <v>89</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D23" s="3"/>
     </row>
@@ -4273,7 +4279,7 @@
         <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D24" s="3"/>
     </row>
